--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_268_R27.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_268_R27.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9688</v>
+        <v>3.7431</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2719</v>
+        <v>1.7437</v>
       </c>
       <c r="F2" t="n">
-        <v>1.697</v>
+        <v>1.9994</v>
       </c>
       <c r="G2" t="n">
         <v>1.8806</v>
@@ -610,13 +610,13 @@
         <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6435999999999999</v>
+        <v>0.1307</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1019</v>
+        <v>0.3699</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5416</v>
+        <v>-0.2392</v>
       </c>
       <c r="V2" t="n">
         <v>-0.8197</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. IZUNDU</t>
+          <t>J. BUTLER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4818</v>
+        <v>1.6602</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2075</v>
+        <v>1.339</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2743</v>
+        <v>0.3212</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0924</v>
+        <v>0.3274</v>
       </c>
       <c r="H3" t="n">
-        <v>0.012</v>
+        <v>0.8162</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0804</v>
+        <v>-0.4888</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8861</v>
+        <v>0.4812</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5917</v>
+        <v>0.5986</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2944</v>
+        <v>-0.1174</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7937</v>
+        <v>-0.1538</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5796</v>
+        <v>0.2175</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.214</v>
+        <v>-0.3713</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9254</v>
+        <v>-0.1131</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4812</v>
+        <v>0.2675</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5557</v>
+        <v>-0.3806</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. BOLOMBOY</t>
+          <t>D. DAVIDOVAC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1529</v>
+        <v>1.1314</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6147</v>
+        <v>1.3372</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5382</v>
+        <v>-0.2058</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-0.0716</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1884</v>
+        <v>-0.3025</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3179</v>
+        <v>0.2309</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.3278</v>
+        <v>1.2114</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.4383</v>
+        <v>0.0336</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1104</v>
+        <v>1.1778</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4574</v>
+        <v>-1.283</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2499</v>
+        <v>-0.3361</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2075</v>
+        <v>-0.9469</v>
       </c>
       <c r="P4" t="n">
         <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3195</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1678</v>
+        <v>0.2752</v>
       </c>
       <c r="T4" t="n">
-        <v>3.3343</v>
+        <v>0.1259</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1665</v>
+        <v>0.1494</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. BUTLER</t>
+          <t>E. IZUNDU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0384</v>
+        <v>0.8955</v>
       </c>
       <c r="E5" t="n">
-        <v>0.482</v>
+        <v>0.5876</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5564</v>
+        <v>0.3079</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3274</v>
+        <v>0.0924</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8162</v>
+        <v>0.012</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4888</v>
+        <v>0.0804</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4812</v>
+        <v>0.8861</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5986</v>
+        <v>0.5917</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1174</v>
+        <v>0.2944</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1538</v>
+        <v>-0.7937</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2175</v>
+        <v>-0.5796</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3713</v>
+        <v>-0.214</v>
       </c>
       <c r="P5" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7349</v>
+        <v>0.3391</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5895</v>
+        <v>0.8612</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1454</v>
+        <v>-0.5221</v>
       </c>
       <c r="V5" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. DAVIDOVAC</t>
+          <t>S. OJELEYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.0395</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0699</v>
+        <v>1.1217</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-1.0822</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0716</v>
+        <v>1.3138</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3025</v>
+        <v>2.4982</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2309</v>
+        <v>-1.1844</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2114</v>
+        <v>1.0817</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0336</v>
+        <v>1.684</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1778</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.283</v>
+        <v>0.2322</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3361</v>
+        <v>0.8142</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9469</v>
+        <v>-0.5821</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1423</v>
+        <v>-0.0424</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1415</v>
+        <v>0.7512</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2838</v>
+        <v>-0.7936</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. MONEKE</t>
+          <t>J. BOLOMBOY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.289</v>
+        <v>-0.1725</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0952</v>
+        <v>-1.7443</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8062</v>
+        <v>1.5718</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3311</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1403</v>
+        <v>-1.1884</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1908</v>
+        <v>0.3179</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1998</v>
+        <v>-1.3278</v>
       </c>
       <c r="K7" t="n">
-        <v>2.4269</v>
+        <v>-1.4383</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7729</v>
+        <v>0.1104</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8687</v>
+        <v>0.4574</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2866</v>
+        <v>0.2499</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5821</v>
+        <v>0.2075</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.871</v>
+        <v>-1.3917</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7834</v>
+        <v>2.3195</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.8424</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1019</v>
+        <v>0.9752</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0359</v>
+        <v>-0.1329</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4665</v>
+        <v>-1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. OJELEYE</t>
+          <t>C. MONEKE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3464</v>
+        <v>-0.2205</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5004999999999999</v>
+        <v>-0.6234</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8469</v>
+        <v>0.4029</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3138</v>
+        <v>2.3311</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4982</v>
+        <v>2.1403</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1844</v>
+        <v>0.1908</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0817</v>
+        <v>3.1998</v>
       </c>
       <c r="K8" t="n">
-        <v>1.684</v>
+        <v>2.4269</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.7729</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2322</v>
+        <v>-0.8687</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8142</v>
+        <v>-0.2866</v>
       </c>
       <c r="O8" t="n">
         <v>-0.5821</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6959</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3195</v>
+        <v>-4.871</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6237</v>
+        <v>2.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4283</v>
+        <v>1.0025</v>
       </c>
       <c r="T8" t="n">
-        <v>0.13</v>
+        <v>0.3699</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5583</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5361</v>
+        <v>-1.4665</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6083</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X8" t="n">
         <v>-2.1444</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1923</v>
+        <v>-0.7433</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.409</v>
+        <v>-3.9936</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2167</v>
+        <v>3.2503</v>
       </c>
       <c r="G9" t="n">
         <v>2.1442</v>
@@ -1156,13 +1156,13 @@
         <v>3.2473</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9474</v>
+        <v>-0.4984</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.187</v>
+        <v>0.2284</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7604</v>
+        <v>-0.7268</v>
       </c>
       <c r="V9" t="n">
         <v>0.3943</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0675</v>
+        <v>-2.7666</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6625</v>
+        <v>-1.3952</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.405</v>
+        <v>-1.3714</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6443</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1191</v>
+        <v>0.1819</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1415</v>
+        <v>0.1259</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9961</v>
+        <v>-3.0709</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.2319</v>
+        <v>-4.8781</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2359</v>
+        <v>1.8072</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3415</v>
@@ -1312,13 +1312,13 @@
         <v>3.2473</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1365</v>
+        <v>-0.2113</v>
       </c>
       <c r="T11" t="n">
-        <v>0.311</v>
+        <v>0.6649</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.4475</v>
+        <v>-0.8762</v>
       </c>
       <c r="V11" t="n">
         <v>-1.214</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2509000000000006</v>
+        <v>0.4958999999999993</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.2521</v>
+        <v>-6.5054</v>
       </c>
       <c r="F12" t="n">
-        <v>7.001399999999999</v>
+        <v>7.001300000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1616</v>
+        <v>3.161600000000001</v>
       </c>
       <c r="H12" t="n">
         <v>1.5726</v>
@@ -1369,13 +1369,13 @@
         <v>1.078</v>
       </c>
       <c r="L12" t="n">
-        <v>4.515899999999999</v>
+        <v>4.515900000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-2.4321</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4946</v>
+        <v>0.4946000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>-2.9268</v>
@@ -1390,13 +1390,13 @@
         <v>20.8756</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1597</v>
+        <v>1.9066</v>
       </c>
       <c r="T12" t="n">
-        <v>3.993199999999999</v>
+        <v>4.74</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.8333</v>
+        <v>-2.8334</v>
       </c>
       <c r="V12" t="n">
         <v>-4.5724</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.049099999999999</v>
+        <v>7.4365</v>
       </c>
       <c r="E13" t="n">
-        <v>5.9093</v>
+        <v>4.8477</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1399</v>
+        <v>2.5888</v>
       </c>
       <c r="G13" t="n">
         <v>1.8557</v>
@@ -1468,13 +1468,13 @@
         <v>3.9432</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8171</v>
+        <v>0.2045</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9663</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.1492</v>
+        <v>-0.7002</v>
       </c>
       <c r="V13" t="n">
         <v>3.7527</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2242</v>
+        <v>3.1118</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8406</v>
+        <v>2.2457</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3836</v>
+        <v>0.8661</v>
       </c>
       <c r="G14" t="n">
         <v>0.3326</v>
@@ -1546,13 +1546,13 @@
         <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8014</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>3.6804</v>
+        <v>1.0855</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.879</v>
+        <v>-0.3965</v>
       </c>
       <c r="V14" t="n">
         <v>0.9304</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. SORKIN</t>
+          <t>J. CLARK III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0856</v>
+        <v>0.8217</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.9772</v>
+        <v>0.0158</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8917</v>
+        <v>0.8058</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.6443</v>
+        <v>3.8947</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.3159</v>
+        <v>2.2217</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3284</v>
+        <v>1.6729</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.9615</v>
+        <v>5.6568</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.4795</v>
+        <v>2.6656</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.482</v>
+        <v>2.9911</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6828</v>
+        <v>-1.7621</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1636</v>
+        <v>-0.4439</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8464</v>
+        <v>-1.3182</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6237</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3195</v>
+        <v>-5.7988</v>
       </c>
       <c r="R15" t="n">
-        <v>3.9432</v>
+        <v>3.0154</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1154</v>
+        <v>-0.4314</v>
       </c>
       <c r="T15" t="n">
-        <v>0.948</v>
+        <v>0.016</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1674</v>
+        <v>-0.4474</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8197</v>
+        <v>0.1418</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3558</v>
+        <v>0.1418</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.301</v>
+        <v>-0.0823</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1168</v>
+        <v>0.0011</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1842</v>
+        <v>-0.0834</v>
       </c>
       <c r="G16" t="n">
         <v>-0.3682</v>
@@ -1702,13 +1702,13 @@
         <v>0.232</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1647</v>
+        <v>0.054</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0593</v>
+        <v>0.1601</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CLARK III</t>
+          <t>R. SORKIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5652</v>
+        <v>-0.4274</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0457</v>
+        <v>-3.3311</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4805</v>
+        <v>2.9037</v>
       </c>
       <c r="G17" t="n">
-        <v>3.8947</v>
+        <v>-3.6443</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2217</v>
+        <v>-2.3159</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6729</v>
+        <v>-1.3284</v>
       </c>
       <c r="J17" t="n">
-        <v>5.6568</v>
+        <v>-2.9615</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6656</v>
+        <v>-2.4795</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9911</v>
+        <v>-0.482</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7621</v>
+        <v>-0.6828</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4439</v>
+        <v>0.1636</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3182</v>
+        <v>-0.8464</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.7834</v>
+        <v>1.6237</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.7988</v>
+        <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
-        <v>3.0154</v>
+        <v>3.9432</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8183</v>
+        <v>0.7736</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0455</v>
+        <v>0.5941</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7727000000000001</v>
+        <v>0.1795</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1418</v>
+        <v>0.8197</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1418</v>
+        <v>1.3558</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. DIBARTOLOMEO</t>
+          <t>I. LUNDBERG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0101</v>
+        <v>-0.468</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.308</v>
+        <v>-3.7502</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2979</v>
+        <v>3.2822</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2532</v>
+        <v>-1.9924</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0323</v>
+        <v>-1.8619</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2208</v>
+        <v>-0.1305</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.0894</v>
+        <v>-2.6213</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3361</v>
+        <v>-2.6545</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.4255</v>
+        <v>0.0333</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.6289</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3684</v>
+        <v>0.7927</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2046</v>
+        <v>-0.1638</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4639</v>
+        <v>4.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0611</v>
+        <v>-0.3312</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0589</v>
+        <v>0.1184</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0022</v>
+        <v>-0.4496</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SANTOS</t>
+          <t>J. DIBARTOLOMEO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4489</v>
+        <v>-0.4704</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3479</v>
+        <v>-1.6003</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7967</v>
+        <v>1.1299</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0023</v>
+        <v>-0.2532</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5666</v>
+        <v>-0.0323</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5689</v>
+        <v>-0.2208</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4275</v>
+        <v>-1.0894</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1982</v>
+        <v>0.3361</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6257</v>
+        <v>-1.4255</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4252</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="N19" t="n">
         <v>-0.3684</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0568</v>
+        <v>1.2046</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0127</v>
+        <v>0.4786</v>
       </c>
       <c r="T19" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.6488</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0048</v>
+        <v>-0.1702</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9299</v>
+        <v>-1.6103</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4093</v>
+        <v>-2.2914</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4794</v>
+        <v>0.6811</v>
       </c>
       <c r="G20" t="n">
         <v>-1.013</v>
@@ -2014,13 +2014,13 @@
         <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9348</v>
+        <v>-0.6152</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4402</v>
+        <v>-0.3222</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4946</v>
+        <v>-0.293</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6778999999999999</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. LUNDBERG</t>
+          <t>M. SANTOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0464</v>
+        <v>-1.7006</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.0477</v>
+        <v>0.4658</v>
       </c>
       <c r="F21" t="n">
-        <v>3.0012</v>
+        <v>-2.1664</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9924</v>
+        <v>0.0023</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8619</v>
+        <v>-0.5666</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1305</v>
+        <v>0.5689</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.6213</v>
+        <v>0.4275</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.6545</v>
+        <v>-0.1982</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0333</v>
+        <v>0.6257</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6289</v>
+        <v>-0.4252</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7927</v>
+        <v>-0.3684</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1638</v>
+        <v>-0.0568</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8556</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>4.1751</v>
+        <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.9096</v>
+        <v>-0.239</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1791</v>
+        <v>0.1259</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7305</v>
+        <v>-0.3648</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W21" t="n">
         <v>1.0722</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.6354</v>
+        <v>-4.7875</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1943</v>
+        <v>-3.6046</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4411</v>
+        <v>-1.183</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9759</v>
@@ -2170,13 +2170,13 @@
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0179</v>
+        <v>-0.17</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8215</v>
+        <v>-0.2317</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1964</v>
+        <v>0.0617</v>
       </c>
       <c r="V22" t="n">
         <v>0.1418</v>
@@ -2203,34 +2203,34 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.250799999999999</v>
+        <v>1.823499999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.001199999999999</v>
+        <v>-7.001500000000002</v>
       </c>
       <c r="F23" t="n">
-        <v>7.2522</v>
+        <v>8.8248</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.161700000000001</v>
+        <v>-3.161699999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.5727</v>
+        <v>-1.572700000000001</v>
       </c>
       <c r="I23" t="n">
         <v>-1.589</v>
       </c>
       <c r="J23" t="n">
-        <v>2.432099999999999</v>
+        <v>2.4321</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4945999999999997</v>
+        <v>-0.4946000000000002</v>
       </c>
       <c r="L23" t="n">
         <v>2.9267</v>
       </c>
       <c r="M23" t="n">
-        <v>-5.593900000000001</v>
+        <v>-5.5939</v>
       </c>
       <c r="N23" t="n">
         <v>-1.078</v>
@@ -2239,31 +2239,31 @@
         <v>-4.5159</v>
       </c>
       <c r="P23" t="n">
-        <v>0.000199999999999978</v>
+        <v>0.0002000000000004221</v>
       </c>
       <c r="Q23" t="n">
         <v>-20.8758</v>
       </c>
       <c r="R23" t="n">
-        <v>20.87580000000001</v>
+        <v>20.8758</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.159799999999999</v>
+        <v>0.4129</v>
       </c>
       <c r="T23" t="n">
-        <v>2.833400000000001</v>
+        <v>2.8334</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.993100000000001</v>
+        <v>-2.4204</v>
       </c>
       <c r="V23" t="n">
-        <v>4.5724</v>
+        <v>4.572399999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>8.608700000000001</v>
+        <v>8.608699999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>-4.036300000000001</v>
+        <v>-4.0363</v>
       </c>
     </row>
   </sheetData>
